--- a/ecom-pdh/03_test-cases/functional/chucnang_checkout/AI_ISC_ecom-pdh_v1.1_TC_dangkyUF_v1.0.xlsx
+++ b/ecom-pdh/03_test-cases/functional/chucnang_checkout/AI_ISC_ecom-pdh_v1.1_TC_dangkyUF_v1.0.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DangKy_UltraFast" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DangKy_UltraFast" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G17" s="39" t="inlineStr">
         <is>
-          <t>- Hiển thị thông báo lỗi: "Số điện thoại chưa đúng, mời nhập lại"
+          <t>- Hiển thị thông báo lỗi: "Số điện thoại không đúng"
 - Border đỏ xuất hiện quanh textbox</t>
         </is>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="41" t="inlineStr">
         <is>
-          <t>Update: BA đổi text lỗi SĐT sai định dạng "Số điện thoại không hợp lệ." -&gt; "Số điện thoại chưa đúng, mời nhập lại" (2026-05-30)</t>
+          <t>Update: BA đổi text lỗi SĐT sai định dạng "Số điện thoại không hợp lệ." -&gt; "Số điện thoại chưa đúng, mời nhập lại" (2026-05-30) -&gt; "Số điện thoại không đúng" (2026-06-11)</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G18" s="39" t="inlineStr">
         <is>
-          <t>- Hiển thị thông báo lỗi: "Số điện thoại chưa đúng, mời nhập lại"
+          <t>- Hiển thị thông báo lỗi: "Số điện thoại không đúng"
 - Border đỏ xuất hiện quanh textbox</t>
         </is>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="41" t="inlineStr">
         <is>
-          <t>Update: BA đổi text lỗi SĐT sai định dạng "Số điện thoại không hợp lệ." -&gt; "Số điện thoại chưa đúng, mời nhập lại" (2026-05-30)</t>
+          <t>Update: BA đổi text lỗi SĐT sai định dạng "Số điện thoại không hợp lệ." -&gt; "Số điện thoại chưa đúng, mời nhập lại" (2026-05-30) -&gt; "Số điện thoại không đúng" (2026-06-11)</t>
         </is>
       </c>
     </row>
